--- a/backtest_runs/20260410_193731/by_symbol/FEM/FEM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FEM/FEM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-3182.399999999997</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>103182.4</v>
@@ -633,7 +633,7 @@
         <v>-3549.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99632.8</v>
@@ -679,7 +679,7 @@
         <v>-4406.400000000004</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>95226.40000000001</v>
@@ -771,7 +771,7 @@
         <v>-5140.799999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>99388</v>
@@ -817,7 +817,7 @@
         <v>-122.3999999999974</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>99265.60000000001</v>
@@ -863,7 +863,7 @@
         <v>-6976.800000000004</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>92288.8</v>
@@ -1185,7 +1185,7 @@
         <v>-1101.599999999998</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>106364.8</v>
@@ -1231,7 +1231,7 @@
         <v>-5752.799999999997</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>100612</v>
@@ -1277,7 +1277,7 @@
         <v>-8935.200000000004</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>91676.8</v>
@@ -1415,7 +1415,7 @@
         <v>-3672.000000000009</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>95348.79999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-2203.200000000018</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>95715.99999999999</v>
